--- a/src/core/xlsx/__fixtures__/excel-slicer-timeline.xlsx
+++ b/src/core/xlsx/__fixtures__/excel-slicer-timeline.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{418D9624-3766-44C0-8D06-E0DAFD6F8AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CBB2167-CB9D-4A18-98B9-790A8B3ADED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="2200" windowHeight="1120" xr2:uid="{11DF6B66-510F-485A-A1DE-20E6F401B2E6}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="2200" windowHeight="1120" xr2:uid="{126EDA2A-C9A1-454A-A1F4-590B0D3A12C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -168,7 +168,7 @@
             <xdr:cNvPr id="2" name="Day">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AB9B0BF-32D1-0C15-0671-EFE74D6AD4C4}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBF91177-FF09-4022-4151-560C1313D172}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Fixture Author" refreshedDate="46310.662183449072" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="6" xr:uid="{027F8D72-0CB4-47F5-8660-C99E79053519}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Fixture Author" refreshedDate="46310.68570613426" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="6" xr:uid="{F53F3AEC-7E7F-4575-BEBB-0B33079E2B43}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D7" sheet="Data"/>
   </cacheSource>
@@ -260,7 +260,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition pivotCacheId="1380037648"/>
+      <x14:pivotCacheDefinition pivotCacheId="1984548742"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -308,7 +308,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AB1E2F64-0011-4D01-B054-81D7A170925A}" name="SalesPivot" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DBBCBF06-02F8-4BA0-904F-D4375C1CA5A1}" name="SalesPivot" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -369,13 +369,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EC2D0997-EF1A-474E-AC7D-6807D27D2E4D}" name="Sales" displayName="Sales" ref="A1:D7" totalsRowShown="0">
-  <autoFilter ref="A1:D7" xr:uid="{EC2D0997-EF1A-474E-AC7D-6807D27D2E4D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{74AEA63E-A132-4663-91E6-BE4543CA8E39}" name="Sales" displayName="Sales" ref="A1:D7" totalsRowShown="0">
+  <autoFilter ref="A1:D7" xr:uid="{74AEA63E-A132-4663-91E6-BE4543CA8E39}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{70D7A25E-EC23-4056-81E0-999F34C3F57D}" name="Category"/>
-    <tableColumn id="2" xr3:uid="{A8A6CF51-08EF-47A2-9E92-FE14D82A5B99}" name="Region"/>
-    <tableColumn id="3" xr3:uid="{2FC53DFD-1942-4567-9C27-E6E4229F54BD}" name="Amount"/>
-    <tableColumn id="4" xr3:uid="{1DC947F0-AF56-4DB8-82F5-B197CF045921}" name="Day" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{C628EAD7-BA5B-4CD1-86F5-188A1FD7EECF}" name="Category"/>
+    <tableColumn id="2" xr3:uid="{37527B73-7AED-402B-9048-48CAE92D73DC}" name="Region"/>
+    <tableColumn id="3" xr3:uid="{319BC6BA-E0DC-4BB1-A144-E54431E8A54D}" name="Amount"/>
+    <tableColumn id="4" xr3:uid="{29EAEDB4-7ACF-41E7-BC71-E8EACE63EB1A}" name="Day" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -697,11 +697,11 @@
 </file>
 
 <file path=xl/timelineCaches/timelineCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<timelineCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="xr10" name="Day" xr10:uid="{4E51F6A2-F9D6-44DD-B3B2-8D37DE828985}" sourceName="Day">
+<timelineCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="xr10" name="Day" xr10:uid="{B35B3208-DC32-4C53-89D8-3B5B5ADCBC46}" sourceName="Day">
   <pivotTables>
     <pivotTable tabId="2" name="SalesPivot"/>
   </pivotTables>
-  <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="1380037648" filterType="unknown">
+  <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="1984548742" filterType="unknown">
     <bounds startDate="2025-01-01T00:00:00" endDate="2026-01-01T00:00:00"/>
   </state>
 </timelineCacheDefinition>
@@ -709,12 +709,12 @@
 
 <file path=xl/timelines/timeline1.xml><?xml version="1.0" encoding="utf-8"?>
 <timelines xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <timeline name="Day" xr10:uid="{9256B5B8-C05D-4340-86D1-D46F2A7478F9}" cache="Day" caption="Day" level="2" selectionLevel="2" scrollPosition="2025-02-19T00:00:00"/>
+  <timeline name="Day" xr10:uid="{6FD6A3EF-7E9E-445D-9753-F83B04E88758}" cache="Day" caption="Day" level="2" selectionLevel="2" scrollPosition="2025-02-19T00:00:00"/>
 </timelines>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF5006C3-0952-420E-95C9-C6027DDF210D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE554C7F-839A-4F3A-B47F-98BCF49E5B72}">
   <dimension ref="A3:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -776,7 +776,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D31EDA9-9DA4-49BC-BDE3-E5139EC0CE2B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7532552-8A36-4A64-82E0-628046FD4ADC}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
